--- a/令和8年度鹿児島県地域課題解決型衛星データ活用実証事業_工数入力用.xlsx
+++ b/令和8年度鹿児島県地域課題解決型衛星データ活用実証事業_工数入力用.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="250">
   <si>
     <t xml:space="preserve">地域課題解決型課題</t>
   </si>
@@ -48,6 +48,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">課題</t>
     </r>
@@ -69,6 +70,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　デキスパートによる写真の自動仕分け</t>
     </r>
@@ -90,6 +92,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　役所からもらえるデータ（図面や設計書）から施工計画書を作成</t>
     </r>
@@ -111,6 +114,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　災害発生個所のヒートマップを作成し、地域ごとの災害予測</t>
     </r>
@@ -132,6 +136,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　過去の工事データから今回の工事の予算や工期、工事人員や重機等を予測する</t>
     </r>
@@ -153,6 +158,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　現在の災害発見は報告があってから→衛生写真からリアルタイムで災害箇所を発見する</t>
     </r>
@@ -174,6 +180,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　災害写真から役所資料の作成や役所への工事のプラン作成</t>
     </r>
@@ -195,6 +202,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　工事中の人数や重機、材料等をリアルタイムで把握し、原価管理アプリ</t>
     </r>
@@ -216,6 +224,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　創意工夫や安全面での課題を過去工事から予測する</t>
     </r>
@@ -237,6 +246,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　過去の工事から類似工事を選択し、点数を上げるためのアイデアを算出する</t>
     </r>
@@ -258,6 +268,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　写真の黒板を工事の流や、現在の作業状況から自動作成する</t>
     </r>
@@ -279,6 +290,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　現場や事務からの課題を収集し、</t>
     </r>
@@ -298,6 +310,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">による仕分けを行う</t>
     </r>
@@ -319,6 +332,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　点群データの自動処理アプリ</t>
     </r>
@@ -343,6 +357,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　施工計画書</t>
     </r>
@@ -367,6 +382,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　材料承認願</t>
     </r>
@@ -388,6 +404,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　施工体制</t>
     </r>
@@ -409,6 +426,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　法面調査報告書</t>
     </r>
@@ -430,6 +448,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　種子計算書</t>
     </r>
@@ -451,6 +470,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　種子管理表</t>
     </r>
@@ -475,6 +495,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　試験練計画書</t>
     </r>
@@ -496,6 +517,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　試験練報告書</t>
     </r>
@@ -517,6 +539,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　創意工夫</t>
     </r>
@@ -538,6 +561,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　出荷証明依頼書</t>
     </r>
@@ -562,6 +586,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　引抜き試験計画書</t>
     </r>
@@ -583,6 +608,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　引抜き試験報告書</t>
     </r>
@@ -604,6 +630,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　写真整理</t>
     </r>
@@ -631,6 +658,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　現場地図メール送信</t>
     </r>
@@ -652,6 +680,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　工事日報チェック・</t>
     </r>
@@ -683,6 +712,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　工事完了報告書</t>
     </r>
@@ -707,6 +737,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　デキスパートデータ</t>
     </r>
@@ -731,6 +762,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　</t>
     </r>
@@ -768,6 +800,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　明日のスケジュール</t>
     </r>
@@ -789,6 +822,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　種子計算書</t>
     </r>
@@ -813,6 +847,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　施工計画書</t>
     </r>
@@ -837,6 +872,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　作業手順書</t>
     </r>
@@ -861,6 +897,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　法面調査報告書</t>
     </r>
@@ -882,6 +919,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　未対応のタスク整理</t>
     </r>
@@ -903,6 +941,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　施工方法マニュアル</t>
     </r>
@@ -924,6 +963,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　法面作業計画書</t>
     </r>
@@ -948,6 +988,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　出面</t>
     </r>
@@ -969,6 +1010,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ダウンロード・保存</t>
     </r>
@@ -990,6 +1032,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　建退共</t>
     </r>
@@ -1011,6 +1054,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ダウンロード・編集・保存</t>
     </r>
@@ -1032,6 +1076,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　</t>
     </r>
@@ -1066,6 +1111,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　グリーンファイル</t>
     </r>
@@ -1087,6 +1133,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">　労務費調査</t>
     </r>
@@ -1111,58 +1158,13 @@
         <color rgb="FF555555"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">懸賞案件の「効果」を書くために、各作業にどれだけ時間がかかっているかを把握します。黄色のセルにご記入ください。年間工数は自動で計算されます。</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">記入欄＝黄色　／　自動計算＝灰色　／　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目は記入例です（実際の記入は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目から）　※ わかる範囲で構いません。概算で結構です。</t>
-    </r>
+    <t xml:space="preserve">記入欄＝黄色　／　自動計算＝灰色　／　4行目は記入例です（実際の記入は5行目から）　※ わかる範囲で構いません。概算で結構です。</t>
   </si>
   <si>
     <t xml:space="preserve">分類</t>
@@ -1175,68 +1177,448 @@
   </si>
   <si>
     <t xml:space="preserve">作業内容</t>
+  </si>
+  <si>
+    <t xml:space="preserve">頻度
+(回/月)</t>
   </si>
   <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">頻度
-</t>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">回あたり
+</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回</t>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">分</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">担当
+人数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間工数
+(時間)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自動化の
+余地</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備考（やりにくい点・時間がかかる理由）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">施工計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">高</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前工事からの転記が多く、毎回同じ内容を打ち直している</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">材料承認願</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">施工体制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法面調査報告書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">種子計算書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">種子管理表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験練計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試験練報告書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">創意工夫</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出荷証明依頼書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">引抜き試験計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">引抜き試験報告書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">写真整理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現場地図メール送信</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工事日報チェック・DL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工事完了報告書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デキスパートデータ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SiteBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">明日のスケジュール</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作業手順書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未対応のタスク整理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">施工方法マニュアル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">法面作業計画書</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出面</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ダウンロード・保存</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">建退共</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CB</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ダウンロード・編集・保存</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buildee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">グリーンファイル</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">労務費調査</t>
+  </si>
+  <si>
+    <t xml:space="preserve">合計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間合計 →</t>
+  </si>
+  <si>
+    <t xml:space="preserve">計算式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">年間工数(時間) ＝ 頻度(回/月) × 12ヶ月 × 1回あたり(分) × 担当人数 ÷ 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">※ 出典：作業項目は「AI課題NEDO事務」シート（葉月工業 生野様 作成）。工数は記入者による実績・概算。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">課題 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">項目の整理</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NEDO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">懸賞案件として出す順番を決めるための整理表です。「現状」と「データの有無」は事実を記入済みです。黄色の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">列（効果・実現性）にご評価をご記入ください。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">記入欄＝黄色（5段階：5が最も高い）　／　自動計算＝灰色　／　4行目は記入例です（実際の記入は5行目から）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">課題</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現状</t>
+  </si>
+  <si>
+    <t xml:space="preserve">使えるデータ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">効果
+(1-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">実現性
+(1-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">総合点
+(効果×実現性)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">備考</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技術的な難易度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技術面の見立て（詰まる所）</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">テーマ</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
@@ -1253,10 +1635,12 @@
         <sz val="10"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回あたり
-</t>
-    </r>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">への適合</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -1265,7 +1649,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">11</t>
     </r>
     <r>
       <rPr>
@@ -1273,1246 +1657,1107 @@
         <sz val="10"/>
         <rFont val="Noto Sans CJK JP"/>
         <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分</t>
-    </r>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">月末のデモ動画を作れるか</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">（記入例）作業日報の自動集計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">構想</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（日報データ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">効果は大きいが、様式がばらばらで整備に時間がかかる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">低</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（記入例）様式が揃っていれば単純な集計で済む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デキスパートによる写真の自動仕分け</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（既存の写真データ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仕分け済みの写真がもらえるなら、画像分類とOCRで素直に作れる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">作れる
+事務負担の削減に直結。画像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">が主で、国産基盤モデルへの貢献はやや弱い。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">役所からもらえるデータ（図面や設計書）から施工計画書を作成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一部あり（発注図・設計書）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">今井様の依頼①で収集中の設計図データが該当</t>
+  </si>
+  <si>
+    <t xml:space="preserve">過去の施工計画書がもらえるなら、LLMで作れる。蓄積がそのまま資産になる。12項目で最も筋がいい。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">◎</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">作れる
+書類作成という業務プロセスそのものの作り直し。国産</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を使う話にできる。テーマとの相性が最も良い。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">災害発生個所のヒートマップを作成し、地域ごとの災害予測</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（過去工事一覧322件）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">県実証事業（衛星データ）と重なる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工事位置の可視化は即できる。ただし「災害予測」には災害の発生実績が要る（工事履歴は災害履歴ではない）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">△</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作れる（可視化まで）
+防災寄りで、業務プロセス改革という切り口からは外れる。県の実証事業と重複。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">過去の工事データから今回の工事の予算や工期、工事人員や重機等を予測する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（過去工事の実績）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">データをもらっても件数は増えない。322件を工種で分けると実質数十件で、予測モデルには足りない。「予測」ではなく「過去の類似工事の実績を並べる」なら確実にできる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">×</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">難しい
+件数不足で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">月末までに動くものを作れない。今回は見送り。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">衛星写真からリアルタイムで災害箇所を発見する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要調達（衛星画像）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">県実証事業の本体テーマ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前提の見直し</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分単位のリアルタイムは衛星では原理的に不可能（再訪周期の制約）。商用SARで数時間〜1日の準リアルタイムなら可能だが費用がかかる。言葉の定義から見直しが要る。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">難しい
+衛星の再訪周期の制約。テーマ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">でもなく、今回のテーマからは外れる。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">災害写真から役所資料の作成や工事プラン作成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（災害写真）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">提出様式が決まっていればLLMで作れる。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">作れる
+災害対応の書類作成。人手不足の現場で効く。国産</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LLM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">の用途として素直。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">工事中の人数・重機・材料をリアルタイムで把握する原価管理アプリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要整備（現場からの入力が要る）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技術ではなく運用の問題。現場が入力し続けるかで決まる。入力が止まれば機能しない。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">運用次第
+現場の入力が続くかに依存。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">分のデモは作れても、導入効果を示しにくい。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">創意工夫や安全面での課題を過去工事から予測する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（創意工夫の提出実績）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">過去の創意工夫がもらえるなら「類似検索」は確実に作れる。「予測」は言い換えが要る。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作れる
+過去の創意工夫からの類似検索。書類作成支援として組み込める。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">過去工事から類似工事を選び、点数を上げるアイデアを算出する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（過去工事の成績）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「類似工事を出す」は作れる。「点数を上げるアイデアを算出」は正解が定義できず、良し悪しを評価できない。データの量ではなく、問いの立て方の問題。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">難しい
+正解が定義できず、効果を数字で示せない。今回は見送り。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">写真の黒板を工事の流れや作業状況から自動作成する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工程と写真の突き合わせ。ルールベース＋LLMで作れる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作れる
+写真整理という明確な業務の置き換え。効果を時間で示しやすい。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現場や事務からの課題を収集し、AIによる仕分けを行う</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「事務作業の工数」シートが出発点になる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">テキスト分類。12項目で最も簡単。「事務作業の工数」シートが入力データになる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作れる
+課題収集と仕分け。「事務作業の工数」シートがそのまま入力になる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点群データの自動処理アプリ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">試作あり（動作する実物・公開デモあり）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（過去工事の点群・設計データ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">変換から出来形の合否判定・帳票出力まで動作。国交省「3次元計測技術を用いた出来形管理要領（案）令和8年3月版」様式-31-2 に準拠。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—（試作済み）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ビューアは動作済み。懸賞に出すなら未解決の3点＝前処理の自動化・2次元図面からの3次元設計面生成・経年比較。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">既にある
+動く実物と公開デモが既にある。技術の優位性を示しやすい。ただし国産基盤モデルへの貢献は弱いので、事務側の項目と組み合わせるのが良い。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">注記</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="10"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">【前提】過去の工事データは葉月工業から提供いただける見込み（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">担当
-人数</t>
-  </si>
-  <si>
+      <t xml:space="preserve">2026/9/24 </t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年間工数
-</t>
-    </r>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">時点）。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【技術的な難易度の見かた】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　低 … 既存の技術で素直に作れる。データが揃えば着手できる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　中 … 作れるが、何を出力とするかの詰めが要る。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　高 … データをもらっても解けない。件数が足りないか、何を正解とするかが決められない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　前提の見直し … そのままでは実現できない。言葉の定義か運用の前提を変える必要がある。</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
-        <sz val="10"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">【</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">NEDO</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">懸賞金活用型プログラム／</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GENIAC-PRIZE 2026 </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">について】</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://www.nedo.go.jp/koubo/CD2_100446.html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　／　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">https://geniac-prize.nedo.go.jp/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　応募者は「課題を解く側」。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">NEDO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">がテーマを出し、応募者が解決策を提案する。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　テーマ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">「エッセンシャルワーカーの人手不足解消に資する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">を活用した業務プロセス改革」賞金</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">億円。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　想定分野に国土交通が含まれており、建設業はテーマの中心に近い。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　提出　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">(</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時間</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">水</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">自動化の
-余地</t>
-  </si>
-  <si>
-    <t xml:space="preserve">備考（やりにくい点・時間がかかる理由）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施工計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">高</t>
-  </si>
-  <si>
-    <t xml:space="preserve">前工事からの転記が多く、毎回同じ内容を打ち直している</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">材料承認願</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施工体制</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法面調査報告書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">種子計算書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">種子管理表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">試験練計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">試験練報告書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">創意工夫</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">出荷証明依頼書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">引抜き試験計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">引抜き試験報告書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">写真整理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現場地図メール送信</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工事日報チェック・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve">)12:00 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">取組概要　／　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">DL</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工事完了報告書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デキスパートデータ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SiteBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">明日のスケジュール</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">作業手順書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未対応のタスク整理</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施工方法マニュアル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">法面作業計画書</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">出面</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">月末 提案書＋デモ動画（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ダウンロード・保存</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">建退共</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">分以内）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　審査　課題設定の妥当性／業務の再設計・導入効果／ユースケースの波及効果／技術の優位性／国産基盤モデル開発への貢献</t>
+  </si>
+  <si>
+    <t xml:space="preserve">【この表の使い方】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　解く側として出すので、「作れるもの・既に動いているもの」を選ぶ。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">CB</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ダウンロード・編集・保存</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buildee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">グリーンファイル</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">労務費調査</t>
-  </si>
-  <si>
-    <t xml:space="preserve">合計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">年間合計 →</t>
-  </si>
-  <si>
-    <t xml:space="preserve">計算式</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年間工数</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">月末にデモ動画が要るため、</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　形にできない項目は今回は見送る。難易度「高」「前提の見直し」の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">時間</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">項目（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">＝ 頻度</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）がこれに当たる。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　◎ … テーマとの相性が良く、デモも作れる。まずここから。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　○ … 作れる。組み合わせの一部として使える。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　△ … テーマから少し外れる、または効果を示しにくい。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">× … </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">今回は見送り。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【審査観点との対応で足りないもの】</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　「業務の再設計・導入効果」… 「事務作業の工数」シートが埋まれば、削減時間を数字で書ける。最優先。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　「国産基盤モデル開発への貢献」… </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">No.12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（点群）単体では弱い。書類作成（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">No.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）と組み合わせる。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　「ユースケースの波及効果」… 法面工事と自治体の点群閲覧は全国共通の課題。長崎県・和歌山県の先行例が使える。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　※ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
     <r>
       <rPr>
-        <sz val="10"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">) × 12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ヶ月 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">× 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">回あたり</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">分</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">) × </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">担当人数 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">÷ 60</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">※ 出典：作業項目は「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">課題</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NEDO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">事務」シート（葉月工業 生野様 作成）。工数は記入者による実績・概算。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">課題 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="14"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">項目の整理</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF555555"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NEDO </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">懸賞案件として出す順番を決めるための整理表です。「現状」と「データの有無」は事実を記入済みです。黄色の</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF555555"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列（効果・実現性）にご評価をご記入ください。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">記入欄＝黄色（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">段階：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">が最も高い）　／　自動計算＝灰色　／　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目は記入例です（実際の記入は</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF996600"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">行目から）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">課題</t>
-  </si>
-  <si>
-    <t xml:space="preserve">現状</t>
-  </si>
-  <si>
-    <t xml:space="preserve">使えるデータ</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">効果
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1-5)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実現性
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(1-5)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">総合点
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">効果</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">実現性</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">備考</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（記入例）作業日報の自動集計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">構想</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（日報データ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">効果は大きいが、様式がばらばらで整備に時間がかかる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デキスパートによる写真の自動仕分け</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（既存の写真データ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">役所からもらえるデータ（図面や設計書）から施工計画書を作成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一部あり（発注図・設計書）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">今井様の依頼①で収集中の設計図データが該当</t>
-  </si>
-  <si>
-    <t xml:space="preserve">災害発生個所のヒートマップを作成し、地域ごとの災害予測</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">あり（過去工事一覧</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">322</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">件）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">県実証事業（衛星データ）と重なる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">過去の工事データから今回の工事の予算や工期、工事人員や重機等を予測する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（過去工事の実績）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">衛星写真からリアルタイムで災害箇所を発見する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要調達（衛星画像）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">県実証事業の本体テーマ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">災害写真から役所資料の作成や工事プラン作成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（災害写真）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工事中の人数・重機・材料をリアルタイムで把握する原価管理アプリ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要整備（現場からの入力が要る）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">創意工夫や安全面での課題を過去工事から予測する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（創意工夫の提出実績）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">過去工事から類似工事を選び、点数を上げるアイデアを算出する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（過去工事の成績）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">写真の黒板を工事の流れや作業状況から自動作成する</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">現場や事務からの課題を収集し、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">による仕分けを行う</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">「事務作業の工数」シートが出発点になる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">点群データの自動処理アプリ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">試作あり（動作する実物・公開デモあり）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（過去工事の点群・設計データ）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">変換から出来形の合否判定・帳票出力まで動作。国交省「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">次元計測技術を用いた出来形管理要領（案）令和</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月版」様式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">-31-2 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に準拠。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">注記</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・「現状」「使えるデータ」は </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">24</t>
     </r>
     <r>
       <rPr>
         <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日時点の事実を記載。効果・実現性の評価は記入者にお願いしています。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">No.12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">「点群データの自動処理アプリ」は既に動作する試作があります（公開デモ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">: https://ryujiyasu.github.io/tengun-viewer/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">）。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">　構想段階の他項目と違い、実測値・要領との対応まで示せるため、提案材料としては最も手前にあります。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">No.3 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">と </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">No.5 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">は鹿児島県の衛星データ実証事業（採択済み）と内容が重なります。切り分けのご確認をお願いします。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">・出典：課題項目は「</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">課題</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">NEDO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF777777"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」シート（葉月工業 生野様 作成）。</t>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">日時点。効果・実現性の評価は業務実態をご存知の方にお願いしています。</t>
     </r>
   </si>
 </sst>
@@ -2524,12 +2769,13 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2558,6 +2804,7 @@
       <sz val="14"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2571,18 +2818,13 @@
       <color rgb="FF555555"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF996600"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF996600"/>
-      <name val="游ゴシック"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2590,6 +2832,7 @@
       <sz val="10"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2604,6 +2847,7 @@
       <color rgb="FF5A7A5A"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <i val="true"/>
@@ -2617,6 +2861,7 @@
       <sz val="10"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2629,12 +2874,14 @@
       <color rgb="FF0000FF"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -2648,12 +2895,6 @@
       <color rgb="FF777777"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF777777"/>
-      <name val="游ゴシック"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -2664,9 +2905,25 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF5A7A5A"/>
+      <name val="Noto Sans CJK JP"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="Noto Sans CJK JP"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Noto Sans CJK JP"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2674,8 +2931,45 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="游ゴシック"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="Noto Sans CJK JP"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="Noto Sans CJK JP"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="游ゴシック"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF555555"/>
+      <name val="游ゴシック"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2685,25 +2979,67 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6EF"/>
+        <bgColor rgb="FFD9EFE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7F2"/>
+        <bgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9D6"/>
+        <bgColor rgb="FFFFF4E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+        <bgColor rgb="FFF0EFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F1E9"/>
+        <bgColor rgb="FFEAF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF3EC"/>
         <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F7F2"/>
+        <fgColor rgb="FFD9EFE3"/>
+        <bgColor rgb="FFE2F1E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4E0"/>
+        <bgColor rgb="FFFFF9D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE9E7"/>
+        <bgColor rgb="FFF0E6F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0EFEF"/>
         <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF9D6"/>
-        <bgColor rgb="FFF2F7F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFEFEF"/>
-        <bgColor rgb="FFF2F7F2"/>
+        <fgColor rgb="FFF0E6F5"/>
+        <bgColor rgb="FFF0EFEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -2812,7 +3148,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2877,55 +3213,55 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="14" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="15" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2933,19 +3269,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="17" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2953,32 +3293,84 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="10" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -3011,11 +3403,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF9D6"/>
-      <rgbColor rgb="FFDCE6EF"/>
+      <rgbColor rgb="FFE2F1E9"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFDCE6EF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -3025,13 +3417,13 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFEAF3EC"/>
+      <rgbColor rgb="FFD9EFE3"/>
+      <rgbColor rgb="FFFFF4E0"/>
+      <rgbColor rgb="FFF0E6F5"/>
+      <rgbColor rgb="FFF0EFEF"/>
       <rgbColor rgb="FFEFEFEF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFCE9E7"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -3233,12 +3625,12 @@
   <dimension ref="A1:A3"/>
   <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3262,67 +3654,67 @@
   <dimension ref="A1:A14"/>
   <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -3346,17 +3738,17 @@
   <dimension ref="A1:C33"/>
   <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="18" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="16.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="16.92"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="35.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="47.71"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
@@ -3367,7 +3759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="2" t="s">
         <v>18</v>
@@ -3376,7 +3768,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7"/>
       <c r="B5" s="2" t="s">
         <v>19</v>
@@ -3385,7 +3777,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7"/>
       <c r="B6" s="2" t="s">
         <v>20</v>
@@ -3394,7 +3786,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7"/>
       <c r="B7" s="2" t="s">
         <v>21</v>
@@ -3403,7 +3795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7"/>
       <c r="B8" s="2" t="s">
         <v>22</v>
@@ -3412,7 +3804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="7"/>
       <c r="B9" s="2" t="s">
         <v>24</v>
@@ -3421,7 +3813,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7"/>
       <c r="B10" s="2" t="s">
         <v>25</v>
@@ -3430,7 +3822,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="7"/>
       <c r="B11" s="2" t="s">
         <v>26</v>
@@ -3439,7 +3831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7"/>
       <c r="B12" s="2" t="s">
         <v>27</v>
@@ -3448,7 +3840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="7"/>
       <c r="B13" s="2" t="s">
         <v>29</v>
@@ -3457,7 +3849,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7"/>
       <c r="B14" s="2" t="s">
         <v>30</v>
@@ -3466,7 +3858,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7"/>
       <c r="B15" s="2" t="s">
         <v>31</v>
@@ -3475,7 +3867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
         <v>33</v>
       </c>
@@ -3484,14 +3876,14 @@
       </c>
       <c r="C16" s="6"/>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7"/>
       <c r="B17" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7"/>
       <c r="B18" s="2" t="s">
         <v>36</v>
@@ -3500,7 +3892,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7"/>
       <c r="B19" s="2" t="s">
         <v>38</v>
@@ -3509,7 +3901,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
         <v>40</v>
@@ -3518,7 +3910,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>42</v>
       </c>
@@ -3527,7 +3919,7 @@
       </c>
       <c r="C21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7"/>
       <c r="B22" s="2" t="s">
         <v>44</v>
@@ -3536,7 +3928,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7"/>
       <c r="B23" s="2" t="s">
         <v>46</v>
@@ -3545,7 +3937,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7"/>
       <c r="B24" s="2" t="s">
         <v>48</v>
@@ -3554,7 +3946,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7"/>
       <c r="B25" s="2" t="s">
         <v>50</v>
@@ -3563,21 +3955,21 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7"/>
       <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
       <c r="C26" s="8"/>
     </row>
-    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="7"/>
       <c r="B27" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C27" s="8"/>
     </row>
-    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="7"/>
       <c r="B28" s="2" t="s">
         <v>53</v>
@@ -3586,7 +3978,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="7"/>
       <c r="B29" s="2" t="s">
         <v>55</v>
@@ -3595,7 +3987,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="7"/>
       <c r="B30" s="2" t="s">
         <v>57</v>
@@ -3604,7 +3996,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="7"/>
       <c r="B31" s="2" t="s">
         <v>59</v>
@@ -3613,7 +4005,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="7"/>
       <c r="B32" s="2" t="s">
         <v>61</v>
@@ -3622,7 +4014,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
         <v>62</v>
@@ -3654,25 +4046,25 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="5.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="24.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="30.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="9.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="10.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="7.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="11.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="9.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="9.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="45.44"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
         <v>65</v>
       </c>
@@ -3709,7 +4101,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
         <v>15</v>
       </c>
@@ -3742,7 +4134,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
         <v>15</v>
       </c>
@@ -3765,7 +4157,7 @@
       <c r="I7" s="24"/>
       <c r="J7" s="26"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
         <v>15</v>
       </c>
@@ -3788,7 +4180,7 @@
       <c r="I8" s="24"/>
       <c r="J8" s="26"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
         <v>15</v>
       </c>
@@ -3811,7 +4203,7 @@
       <c r="I9" s="24"/>
       <c r="J9" s="26"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
         <v>15</v>
       </c>
@@ -3834,7 +4226,7 @@
       <c r="I10" s="24"/>
       <c r="J10" s="26"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
         <v>15</v>
       </c>
@@ -3857,7 +4249,7 @@
       <c r="I11" s="24"/>
       <c r="J11" s="26"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
         <v>15</v>
       </c>
@@ -3880,7 +4272,7 @@
       <c r="I12" s="24"/>
       <c r="J12" s="26"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
         <v>15</v>
       </c>
@@ -3903,7 +4295,7 @@
       <c r="I13" s="24"/>
       <c r="J13" s="26"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
         <v>15</v>
       </c>
@@ -3926,7 +4318,7 @@
       <c r="I14" s="24"/>
       <c r="J14" s="26"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
         <v>15</v>
       </c>
@@ -3949,7 +4341,7 @@
       <c r="I15" s="24"/>
       <c r="J15" s="26"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
         <v>15</v>
       </c>
@@ -3972,7 +4364,7 @@
       <c r="I16" s="24"/>
       <c r="J16" s="26"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
         <v>15</v>
       </c>
@@ -3995,7 +4387,7 @@
       <c r="I17" s="24"/>
       <c r="J17" s="26"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
         <v>15</v>
       </c>
@@ -4018,7 +4410,7 @@
       <c r="I18" s="24"/>
       <c r="J18" s="26"/>
     </row>
-    <row r="19" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
         <v>15</v>
       </c>
@@ -4041,7 +4433,7 @@
       <c r="I19" s="24"/>
       <c r="J19" s="26"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
         <v>33</v>
       </c>
@@ -4062,7 +4454,7 @@
       <c r="I20" s="24"/>
       <c r="J20" s="26"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
         <v>33</v>
       </c>
@@ -4083,7 +4475,7 @@
       <c r="I21" s="24"/>
       <c r="J21" s="26"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
         <v>33</v>
       </c>
@@ -4106,7 +4498,7 @@
       <c r="I22" s="24"/>
       <c r="J22" s="26"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
         <v>33</v>
       </c>
@@ -4129,7 +4521,7 @@
       <c r="I23" s="24"/>
       <c r="J23" s="26"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
         <v>33</v>
       </c>
@@ -4152,7 +4544,7 @@
       <c r="I24" s="24"/>
       <c r="J24" s="26"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
         <v>42</v>
       </c>
@@ -4173,7 +4565,7 @@
       <c r="I25" s="24"/>
       <c r="J25" s="26"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
         <v>42</v>
       </c>
@@ -4196,7 +4588,7 @@
       <c r="I26" s="24"/>
       <c r="J26" s="26"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
         <v>42</v>
       </c>
@@ -4219,7 +4611,7 @@
       <c r="I27" s="24"/>
       <c r="J27" s="26"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
         <v>42</v>
       </c>
@@ -4242,7 +4634,7 @@
       <c r="I28" s="24"/>
       <c r="J28" s="26"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
         <v>42</v>
       </c>
@@ -4265,7 +4657,7 @@
       <c r="I29" s="24"/>
       <c r="J29" s="26"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
         <v>42</v>
       </c>
@@ -4286,7 +4678,7 @@
       <c r="I30" s="24"/>
       <c r="J30" s="26"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
         <v>42</v>
       </c>
@@ -4307,7 +4699,7 @@
       <c r="I31" s="24"/>
       <c r="J31" s="26"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
         <v>42</v>
       </c>
@@ -4330,7 +4722,7 @@
       <c r="I32" s="24"/>
       <c r="J32" s="26"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
         <v>42</v>
       </c>
@@ -4353,7 +4745,7 @@
       <c r="I33" s="24"/>
       <c r="J33" s="26"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
         <v>42</v>
       </c>
@@ -4376,7 +4768,7 @@
       <c r="I34" s="24"/>
       <c r="J34" s="26"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
         <v>42</v>
       </c>
@@ -4399,7 +4791,7 @@
       <c r="I35" s="24"/>
       <c r="J35" s="26"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
         <v>42</v>
       </c>
@@ -4422,7 +4814,7 @@
       <c r="I36" s="24"/>
       <c r="J36" s="26"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
         <v>42</v>
       </c>
@@ -4445,7 +4837,7 @@
       <c r="I37" s="24"/>
       <c r="J37" s="26"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="28" t="s">
         <v>140</v>
       </c>
@@ -4464,17 +4856,17 @@
       <c r="I38" s="29"/>
       <c r="J38" s="29"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="32" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="33" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="34" t="s">
         <v>144</v>
       </c>
@@ -4495,7 +4887,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:L52"/>
   <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="5.16"/>
@@ -4505,19 +4897,23 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="3" width="8.26"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="3" width="11.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="3" width="47.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="35" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
         <v>147</v>
       </c>
@@ -4547,19 +4943,31 @@
       <c r="H5" s="16" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I5" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
         <v>76</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>4</v>
@@ -4572,297 +4980,570 @@
         <v>12</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>162</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="J6" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
         <v>80</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="37" t="str">
+        <v>166</v>
+      </c>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="40" t="str">
         <f aca="false">IF(COUNT(E7:F7)=2,E7*F7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="38"/>
-    </row>
-    <row r="8" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="41"/>
+      <c r="I7" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="K7" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="L7" s="41" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
         <v>81</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37" t="str">
+        <v>171</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40" t="str">
         <f aca="false">IF(COUNT(E8:F8)=2,E8*F8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="I8" s="42" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J8" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="K8" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="L8" s="41" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="22" t="s">
         <v>83</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="37" t="str">
+        <v>177</v>
+      </c>
+      <c r="E9" s="39"/>
+      <c r="F9" s="39"/>
+      <c r="G9" s="40" t="str">
         <f aca="false">IF(COUNT(E9:F9)=2,E9*F9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="38" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H9" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="J9" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="K9" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="L9" s="41" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="22" t="s">
         <v>85</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="37" t="str">
+        <v>184</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="40" t="str">
         <f aca="false">IF(COUNT(E10:F10)=2,E10*F10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="38"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="41"/>
+      <c r="I10" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="41" t="s">
+        <v>185</v>
+      </c>
+      <c r="K10" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="L10" s="41" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="22" t="s">
         <v>87</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="37" t="str">
+        <v>189</v>
+      </c>
+      <c r="E11" s="39"/>
+      <c r="F11" s="39"/>
+      <c r="G11" s="40" t="str">
         <f aca="false">IF(COUNT(E11:F11)=2,E11*F11,"")</f>
         <v/>
       </c>
-      <c r="H11" s="38" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="41" t="s">
+        <v>190</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="J11" s="41" t="s">
+        <v>192</v>
+      </c>
+      <c r="K11" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="L11" s="41" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="22" t="s">
         <v>89</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="37" t="str">
+        <v>195</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="40" t="str">
         <f aca="false">IF(COUNT(E12:F12)=2,E12*F12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="38"/>
-    </row>
-    <row r="13" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="41"/>
+      <c r="I12" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="J12" s="41" t="s">
+        <v>196</v>
+      </c>
+      <c r="K12" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="L12" s="41" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="22" t="s">
         <v>91</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>174</v>
+        <v>198</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-      <c r="G13" s="37" t="str">
+        <v>199</v>
+      </c>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="40" t="str">
         <f aca="false">IF(COUNT(E13:F13)=2,E13*F13,"")</f>
         <v/>
       </c>
-      <c r="H13" s="38"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="41"/>
+      <c r="I13" s="49" t="s">
+        <v>191</v>
+      </c>
+      <c r="J13" s="41" t="s">
+        <v>200</v>
+      </c>
+      <c r="K13" s="46" t="s">
+        <v>181</v>
+      </c>
+      <c r="L13" s="41" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="s">
         <v>93</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="37" t="str">
+        <v>203</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="40" t="str">
         <f aca="false">IF(COUNT(E14:F14)=2,E14*F14,"")</f>
         <v/>
       </c>
-      <c r="H14" s="38"/>
-    </row>
-    <row r="15" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="41"/>
+      <c r="I14" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="J14" s="41" t="s">
+        <v>204</v>
+      </c>
+      <c r="K14" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="L14" s="41" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="22" t="s">
         <v>95</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>178</v>
+        <v>206</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="37" t="str">
+        <v>207</v>
+      </c>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="40" t="str">
         <f aca="false">IF(COUNT(E15:F15)=2,E15*F15,"")</f>
         <v/>
       </c>
-      <c r="H15" s="38"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="41"/>
+      <c r="I15" s="47" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>208</v>
+      </c>
+      <c r="K15" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="L15" s="41" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="s">
         <v>97</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="37" t="str">
+        <v>166</v>
+      </c>
+      <c r="E16" s="39"/>
+      <c r="F16" s="39"/>
+      <c r="G16" s="40" t="str">
         <f aca="false">IF(COUNT(E16:F16)=2,E16*F16,"")</f>
         <v/>
       </c>
-      <c r="H16" s="38"/>
-    </row>
-    <row r="17" customFormat="false" ht="29.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H16" s="41"/>
+      <c r="I16" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="J16" s="41" t="s">
+        <v>211</v>
+      </c>
+      <c r="K16" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="L16" s="41" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="22" t="s">
         <v>99</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="37" t="str">
+        <v>214</v>
+      </c>
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="40" t="str">
         <f aca="false">IF(COUNT(E17:F17)=2,E17*F17,"")</f>
         <v/>
       </c>
-      <c r="H17" s="38"/>
-    </row>
-    <row r="18" customFormat="false" ht="41" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="39" t="s">
+      <c r="H17" s="41"/>
+      <c r="I17" s="42" t="s">
+        <v>163</v>
+      </c>
+      <c r="J17" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="K17" s="43" t="s">
+        <v>168</v>
+      </c>
+      <c r="L17" s="41" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="C18" s="41" t="s">
-        <v>184</v>
-      </c>
-      <c r="D18" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="37" t="str">
+      <c r="B18" s="51" t="s">
+        <v>217</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="40" t="str">
         <f aca="false">IF(COUNT(E18:F18)=2,E18*F18,"")</f>
         <v/>
       </c>
-      <c r="H18" s="38" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="I18" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="J18" s="41" t="s">
+        <v>222</v>
+      </c>
+      <c r="K18" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="L18" s="41" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34" t="s">
-        <v>192</v>
+        <v>224</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="54"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="55" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="54"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="55" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="54" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="54" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="54" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="54" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="54"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="55" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="54" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="54" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="54" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="54" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="54"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="54" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="54" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="54"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="55" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="54" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="54" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="54" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="54" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="54" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="54" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="54"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="55" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="54" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="54" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="54" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="54"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="54" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/令和8年度鹿児島県地域課題解決型衛星データ活用実証事業_工数入力用.xlsx
+++ b/令和8年度鹿児島県地域課題解決型衛星データ活用実証事業_工数入力用.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="276">
   <si>
     <t xml:space="preserve">地域課題解決型課題</t>
   </si>
@@ -1609,118 +1609,94 @@
     <t xml:space="preserve">技術面の見立て（詰まる所）</t>
   </si>
   <si>
+    <t xml:space="preserve">テーマ1への適合</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">テーマ</t>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">月末のデモ動画を作れるか</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">今後の扱い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開発としてどうするか</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（記入例）作業日報の自動集計</t>
+  </si>
+  <si>
+    <t xml:space="preserve">構想</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（日報データ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">効果は大きいが、様式がばらばらで整備に時間がかかる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">低</t>
+  </si>
+  <si>
+    <t xml:space="preserve">（記入例）様式が揃っていれば単純な集計で済む</t>
+  </si>
+  <si>
+    <t xml:space="preserve">デキスパートによる写真の自動仕分け</t>
+  </si>
+  <si>
+    <t xml:space="preserve">あり（既存の写真データ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仕分け済みの写真がもらえるなら、画像分類とOCRで素直に作れる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">○</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作れる
+事務負担の削減に直結。画像AIが主で、国産基盤モデルへの貢献はやや弱い。</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">への適合</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GENIAC</t>
+    </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">月末のデモ動画を作れるか</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">（記入例）作業日報の自動集計</t>
-  </si>
-  <si>
-    <t xml:space="preserve">構想</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（日報データ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">効果は大きいが、様式がばらばらで整備に時間がかかる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">低</t>
-  </si>
-  <si>
-    <t xml:space="preserve">（記入例）様式が揃っていれば単純な集計で済む</t>
-  </si>
-  <si>
-    <t xml:space="preserve">デキスパートによる写真の自動仕分け</t>
-  </si>
-  <si>
-    <t xml:space="preserve">あり（既存の写真データ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仕分け済みの写真がもらえるなら、画像分類とOCRで素直に作れる。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">○</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">作れる
-事務負担の削減に直結。画像</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">AI</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">が主で、国産基盤モデルへの貢献はやや弱い。</t>
-    </r>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に出す</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">写真の自動仕分け。単独でも成立する。</t>
   </si>
   <si>
     <t xml:space="preserve">役所からもらえるデータ（図面や設計書）から施工計画書を作成</t>
@@ -1738,34 +1714,11 @@
     <t xml:space="preserve">◎</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">作れる
-書類作成という業務プロセスそのものの作り直し。国産</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LLM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">を使う話にできる。テーマとの相性が最も良い。</t>
-    </r>
+    <t xml:space="preserve">作れる
+書類作成という業務プロセスそのものの作り直し。国産LLMを使う話にできる。テーマとの相性が最も良い。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">図面・設計書から施工計画書。過去の施工計画書が資産になる。</t>
   </si>
   <si>
     <t xml:space="preserve">災害発生個所のヒートマップを作成し、地域ごとの災害予測</t>
@@ -1790,6 +1743,12 @@
 防災寄りで、業務プロセス改革という切り口からは外れる。県の実証事業と重複。</t>
   </si>
   <si>
+    <t xml:space="preserve">県の実証事業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工事位置の可視化まではすぐできる。災害予測は県の衛星データ実証事業の側で扱う。</t>
+  </si>
+  <si>
     <t xml:space="preserve">過去の工事データから今回の工事の予算や工期、工事人員や重機等を予測する</t>
   </si>
   <si>
@@ -1802,34 +1761,14 @@
     <t xml:space="preserve">×</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">難しい
-件数不足で</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">11</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">月末までに動くものを作れない。今回は見送り。</t>
-    </r>
+    <t xml:space="preserve">難しい
+件数不足で11月末までに動くものを作れない。今回は見送り。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">開発する</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「予測」ではなく「過去の類似工事の実績を並べる」として作る。No.8・No.9 と同じ基盤（過去工事の検索・参照）で 3項目まとめて満たせる。</t>
   </si>
   <si>
     <t xml:space="preserve">衛星写真からリアルタイムで災害箇所を発見する</t>
@@ -1847,34 +1786,11 @@
     <t xml:space="preserve">分単位のリアルタイムは衛星では原理的に不可能（再訪周期の制約）。商用SARで数時間〜1日の準リアルタイムなら可能だが費用がかかる。言葉の定義から見直しが要る。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">難しい
-衛星の再訪周期の制約。テーマ</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">でもなく、今回のテーマからは外れる。</t>
-    </r>
+    <t xml:space="preserve">難しい
+衛星の再訪周期の制約。テーマ2でもなく、今回のテーマからは外れる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">採択済みの県実証事業の本体テーマ。GENIAC と二重に出さない。なお「リアルタイム」の定義は県事業の中でも見直しが要る。</t>
   </si>
   <si>
     <t xml:space="preserve">災害写真から役所資料の作成や工事プラン作成</t>
@@ -1886,34 +1802,11 @@
     <t xml:space="preserve">提出様式が決まっていればLLMで作れる。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">作れる
-災害対応の書類作成。人手不足の現場で効く。国産</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LLM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">の用途として素直。</t>
-    </r>
+    <t xml:space="preserve">作れる
+災害対応の書類作成。人手不足の現場で効く。国産LLMの用途として素直。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">災害写真から役所資料。人手不足の現場に直接効く。</t>
   </si>
   <si>
     <t xml:space="preserve">工事中の人数・重機・材料をリアルタイムで把握する原価管理アプリ</t>
@@ -1922,37 +1815,14 @@
     <t xml:space="preserve">要整備（現場からの入力が要る）</t>
   </si>
   <si>
-    <t xml:space="preserve">技術ではなく運用の問題。現場が入力し続けるかで決まる。入力が止まれば機能しない。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">運用次第
-現場の入力が続くかに依存。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="游ゴシック"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">分のデモは作れても、導入効果を示しにくい。</t>
-    </r>
+    <t xml:space="preserve">技術的には作れる。現場の全面協力が得られる前提なら、入力が続くかという懸念は解消する。残る論点は入力の軽さ。写真・日報・位置情報など既に発生しているものから自動で拾い、人が打つ項目を最小限にする設計が要る。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作れる
+現場で実際に回して効果を測れるので、導入効果を実測で示せる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">現場の全面協力が得られるため、実証環境としてそのまま使える。入力を最小化する設計にすること。</t>
   </si>
   <si>
     <t xml:space="preserve">創意工夫や安全面での課題を過去工事から予測する</t>
@@ -1968,6 +1838,9 @@
 過去の創意工夫からの類似検索。書類作成支援として組み込める。</t>
   </si>
   <si>
+    <t xml:space="preserve">創意工夫の類似検索。No.4・No.9 と同じ基盤に乗る。</t>
+  </si>
+  <si>
     <t xml:space="preserve">過去工事から類似工事を選び、点数を上げるアイデアを算出する</t>
   </si>
   <si>
@@ -1981,6 +1854,9 @@
 正解が定義できず、効果を数字で示せない。今回は見送り。</t>
   </si>
   <si>
+    <t xml:space="preserve">「点数を上げるアイデアの算出」は作れない。「類似工事を出す」は No.4 と同一機能なので、1つ作れば両方カバーできる。</t>
+  </si>
+  <si>
     <t xml:space="preserve">写真の黒板を工事の流れや作業状況から自動作成する</t>
   </si>
   <si>
@@ -1991,17 +1867,49 @@
 写真整理という明確な業務の置き換え。効果を時間で示しやすい。</t>
   </si>
   <si>
+    <t xml:space="preserve">黒板の自動作成。削減時間を示しやすい。</t>
+  </si>
+  <si>
     <t xml:space="preserve">現場や事務からの課題を収集し、AIによる仕分けを行う</t>
   </si>
   <si>
     <t xml:space="preserve">「事務作業の工数」シートが出発点になる</t>
   </si>
   <si>
-    <t xml:space="preserve">テキスト分類。12項目で最も簡単。「事務作業の工数」シートが入力データになる。</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">テキスト分類。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">項目で最も簡単。現場から課題を出してもらえる前提なら、入力も回る。</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">作れる
-課題収集と仕分け。「事務作業の工数」シートがそのまま入力になる。</t>
+「事務作業の工数」シートがそのまま入力データになる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">課題の収集と仕分け。現場の協力があるので、収集の部分が実際に回る。</t>
   </si>
   <si>
     <t xml:space="preserve">点群データの自動処理アプリ</t>
@@ -2026,6 +1934,9 @@
 動く実物と公開デモが既にある。技術の優位性を示しやすい。ただし国産基盤モデルへの貢献は弱いので、事務側の項目と組み合わせるのが良い。</t>
   </si>
   <si>
+    <t xml:space="preserve">点群。動く実物と公開デモが既にある。</t>
+  </si>
+  <si>
     <t xml:space="preserve">注記</t>
   </si>
   <si>
@@ -2038,7 +1949,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">【前提】過去の工事データは葉月工業から提供いただける見込み（</t>
+      <t xml:space="preserve">【前提】（</t>
     </r>
     <r>
       <rPr>
@@ -2060,23 +1971,32 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">時点）。</t>
-    </r>
+      <t xml:space="preserve">時点）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　・過去の工事データは葉月工業から提供いただける。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　・現場の全面協力が得られる。実証やデータ入力に協力してもらえる。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　→ これは提案上の強みでもある。協力してくれる実証フィールドを持つ応募者は多くない。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　審査観点「業務の再設計・導入効果」を実測で書ける。</t>
   </si>
   <si>
     <t xml:space="preserve">【技術的な難易度の見かた】</t>
   </si>
   <si>
-    <t xml:space="preserve">　低 … 既存の技術で素直に作れる。データが揃えば着手できる。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　中 … 作れるが、何を出力とするかの詰めが要る。</t>
+    <t xml:space="preserve">　低 … 既存の技術で素直に作れる。　中 … 作れるが、何を出力とするかの詰めが要る。</t>
   </si>
   <si>
     <t xml:space="preserve">　高 … データをもらっても解けない。件数が足りないか、何を正解とするかが決められない。</t>
   </si>
   <si>
-    <t xml:space="preserve">　前提の見直し … そのままでは実現できない。言葉の定義か運用の前提を変える必要がある。</t>
+    <t xml:space="preserve">　前提の見直し … そのままでは実現できない。言葉の定義を変える必要がある。</t>
   </si>
   <si>
     <r>
@@ -2121,7 +2041,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">GENIAC-PRIZE 2026 </t>
+      <t xml:space="preserve">GENIAC-PRIZE 2026</t>
     </r>
     <r>
       <rPr>
@@ -2132,7 +2052,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">について】</t>
+      <t xml:space="preserve">】</t>
     </r>
   </si>
   <si>
@@ -2420,27 +2340,199 @@
     <t xml:space="preserve">　審査　課題設定の妥当性／業務の再設計・導入効果／ユースケースの波及効果／技術の優位性／国産基盤モデル開発への貢献</t>
   </si>
   <si>
-    <t xml:space="preserve">【この表の使い方】</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">　解く側として出すので、「作れるもの・既に動いているもの」を選ぶ。</t>
-    </r>
-    <r>
-      <rPr>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">【「今後の扱い」の見かた】　</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <color rgb="FF555555"/>
         <rFont val="游ゴシック"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">GENIAC</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に出さない ＝ 開発しない、ではない。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GENIAC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">に出す（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">項目：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">11</t>
     </r>
     <r>
@@ -2451,19 +2543,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">月末にデモ動画が要るため、</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">　形にできない項目は今回は見送る。難易度「高」「前提の見直し」の</t>
+      <t xml:space="preserve">・</t>
     </r>
     <r>
       <rPr>
@@ -2473,6 +2553,90 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">月末にデモ動画を作れて、テーマにも合う。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　開発する（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">項目：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">4</t>
     </r>
     <r>
@@ -2483,7 +2647,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">項目（</t>
+      <t xml:space="preserve">・</t>
     </r>
     <r>
       <rPr>
@@ -2493,7 +2657,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">4</t>
+      <t xml:space="preserve">8</t>
     </r>
     <r>
       <rPr>
@@ -2513,6 +2677,194 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">GENIAC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">には出さないが自社で作る。この</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">つは「過去工事を検索して、似た工事の実績</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　　（予算・工期・人員・重機・創意工夫）を並べて見せる」という </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">つの基盤で全部満たせる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　　「予測」と言うと機械学習が要り </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">322</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">件では精度が出ないが、「参照」なら検索で済み今すぐ作れる。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　県の実証事業（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">項目：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="游ゴシック"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">5</t>
     </r>
     <r>
@@ -2523,7 +2875,19 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">・</t>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　　採択済みの衛星データ実証事業の側で扱う。</t>
     </r>
     <r>
       <rPr>
@@ -2533,17 +2897,32 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">・</t>
+      <t xml:space="preserve">GENIAC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">と二重に出さない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">【設計上の注意】</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">　</t>
     </r>
     <r>
       <rPr>
@@ -2553,38 +2932,17 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">）がこれに当たる。</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">　◎ … テーマとの相性が良く、デモも作れる。まずここから。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　○ … 作れる。組み合わせの一部として使える。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　△ … テーマから少し外れる、または効果を示しにくい。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">　</t>
+      <t xml:space="preserve">No.7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">（原価管理）… 現場の協力があっても、</t>
     </r>
     <r>
       <rPr>
@@ -2594,18 +2952,24 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">× … </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF555555"/>
-        <rFont val="Noto Sans CJK JP"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">今回は見送り。</t>
-    </r>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF555555"/>
+        <rFont val="Noto Sans CJK JP"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">日に何度も手入力させる作りにすると続かない。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　　協力の意思と作業の手間は別。写真・日報・位置情報など既に発生しているものから自動で拾い、</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　人が打つ項目を最小限にすること。</t>
   </si>
   <si>
     <t xml:space="preserve">【審査観点との対応で足りないもの】</t>
@@ -2926,14 +3290,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b val="true"/>
+      <sz val="12"/>
       <name val="游ゴシック"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="游ゴシック"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2969,7 +3333,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3026,6 +3390,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF0E6F5"/>
+        <bgColor rgb="FFF0EFEF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFCE9E7"/>
         <bgColor rgb="FFF0E6F5"/>
       </patternFill>
@@ -3038,8 +3408,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0E6F5"/>
-        <bgColor rgb="FFF0EFEF"/>
+        <fgColor rgb="FFE8F0FA"/>
+        <bgColor rgb="FFEAF3EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -3148,7 +3518,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3325,6 +3695,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="8" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3341,11 +3715,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="12" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3389,7 +3767,7 @@
       <rgbColor rgb="FFFF0000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFEAF3EC"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -3417,7 +3795,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFEAF3EC"/>
+      <rgbColor rgb="FFE8F0FA"/>
       <rgbColor rgb="FFD9EFE3"/>
       <rgbColor rgb="FFFFF4E0"/>
       <rgbColor rgb="FFF0E6F5"/>
@@ -4887,7 +5265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr defaultColWidth="8.87890625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="5.16"/>
@@ -4901,6 +5279,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="3" width="52"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="3" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="3" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="3" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="3" width="54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4955,19 +5335,25 @@
       <c r="L5" s="17" t="s">
         <v>158</v>
       </c>
+      <c r="M5" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="N5" s="16" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="18" t="s">
         <v>76</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>4</v>
@@ -4980,29 +5366,31 @@
         <v>12</v>
       </c>
       <c r="H6" s="20" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K6" s="38"/>
       <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="22" t="s">
         <v>80</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E7" s="39"/>
       <c r="F7" s="39"/>
@@ -5012,16 +5400,22 @@
       </c>
       <c r="H7" s="41"/>
       <c r="I7" s="42" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J7" s="41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K7" s="43" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L7" s="41" t="s">
-        <v>169</v>
+        <v>171</v>
+      </c>
+      <c r="M7" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="N7" s="41" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5029,13 +5423,13 @@
         <v>81</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E8" s="39"/>
       <c r="F8" s="39"/>
@@ -5044,19 +5438,25 @@
         <v/>
       </c>
       <c r="H8" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="K8" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="L8" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="M8" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="I8" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="J8" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="K8" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="L8" s="41" t="s">
-        <v>175</v>
+      <c r="N8" s="41" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5064,13 +5464,13 @@
         <v>83</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E9" s="39"/>
       <c r="F9" s="39"/>
@@ -5079,19 +5479,25 @@
         <v/>
       </c>
       <c r="H9" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="45" t="s">
-        <v>179</v>
+        <v>183</v>
+      </c>
+      <c r="I9" s="46" t="s">
+        <v>184</v>
       </c>
       <c r="J9" s="41" t="s">
-        <v>180</v>
-      </c>
-      <c r="K9" s="46" t="s">
-        <v>181</v>
+        <v>185</v>
+      </c>
+      <c r="K9" s="47" t="s">
+        <v>186</v>
       </c>
       <c r="L9" s="41" t="s">
-        <v>182</v>
+        <v>187</v>
+      </c>
+      <c r="M9" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="N9" s="41" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5099,13 +5505,13 @@
         <v>85</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="E10" s="39"/>
       <c r="F10" s="39"/>
@@ -5114,17 +5520,23 @@
         <v/>
       </c>
       <c r="H10" s="41"/>
-      <c r="I10" s="47" t="s">
+      <c r="I10" s="49" t="s">
         <v>78</v>
       </c>
       <c r="J10" s="41" t="s">
-        <v>185</v>
-      </c>
-      <c r="K10" s="48" t="s">
-        <v>186</v>
+        <v>192</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>193</v>
       </c>
       <c r="L10" s="41" t="s">
-        <v>187</v>
+        <v>194</v>
+      </c>
+      <c r="M10" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="N10" s="41" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5132,13 +5544,13 @@
         <v>87</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E11" s="39"/>
       <c r="F11" s="39"/>
@@ -5147,19 +5559,25 @@
         <v/>
       </c>
       <c r="H11" s="41" t="s">
-        <v>190</v>
-      </c>
-      <c r="I11" s="49" t="s">
-        <v>191</v>
+        <v>199</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>200</v>
       </c>
       <c r="J11" s="41" t="s">
-        <v>192</v>
-      </c>
-      <c r="K11" s="48" t="s">
-        <v>186</v>
+        <v>201</v>
+      </c>
+      <c r="K11" s="50" t="s">
+        <v>193</v>
       </c>
       <c r="L11" s="41" t="s">
-        <v>193</v>
+        <v>202</v>
+      </c>
+      <c r="M11" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="N11" s="41" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5167,13 +5585,13 @@
         <v>89</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="E12" s="39"/>
       <c r="F12" s="39"/>
@@ -5183,16 +5601,22 @@
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="42" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J12" s="41" t="s">
-        <v>196</v>
-      </c>
-      <c r="K12" s="44" t="s">
-        <v>174</v>
+        <v>206</v>
+      </c>
+      <c r="K12" s="45" t="s">
+        <v>178</v>
       </c>
       <c r="L12" s="41" t="s">
-        <v>197</v>
+        <v>207</v>
+      </c>
+      <c r="M12" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="N12" s="41" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5200,13 +5624,13 @@
         <v>91</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E13" s="39"/>
       <c r="F13" s="39"/>
@@ -5215,17 +5639,23 @@
         <v/>
       </c>
       <c r="H13" s="41"/>
-      <c r="I13" s="49" t="s">
-        <v>191</v>
+      <c r="I13" s="46" t="s">
+        <v>184</v>
       </c>
       <c r="J13" s="41" t="s">
-        <v>200</v>
-      </c>
-      <c r="K13" s="46" t="s">
-        <v>181</v>
+        <v>211</v>
+      </c>
+      <c r="K13" s="43" t="s">
+        <v>170</v>
       </c>
       <c r="L13" s="41" t="s">
-        <v>201</v>
+        <v>212</v>
+      </c>
+      <c r="M13" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="N13" s="41" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5233,13 +5663,13 @@
         <v>93</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="E14" s="39"/>
       <c r="F14" s="39"/>
@@ -5248,17 +5678,23 @@
         <v/>
       </c>
       <c r="H14" s="41"/>
-      <c r="I14" s="45" t="s">
-        <v>179</v>
+      <c r="I14" s="46" t="s">
+        <v>184</v>
       </c>
       <c r="J14" s="41" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="K14" s="43" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L14" s="41" t="s">
-        <v>205</v>
+        <v>217</v>
+      </c>
+      <c r="M14" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="N14" s="41" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5266,13 +5702,13 @@
         <v>95</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="E15" s="39"/>
       <c r="F15" s="39"/>
@@ -5281,17 +5717,23 @@
         <v/>
       </c>
       <c r="H15" s="41"/>
-      <c r="I15" s="47" t="s">
+      <c r="I15" s="49" t="s">
         <v>78</v>
       </c>
       <c r="J15" s="41" t="s">
-        <v>208</v>
-      </c>
-      <c r="K15" s="48" t="s">
-        <v>186</v>
+        <v>221</v>
+      </c>
+      <c r="K15" s="50" t="s">
+        <v>193</v>
       </c>
       <c r="L15" s="41" t="s">
-        <v>209</v>
+        <v>222</v>
+      </c>
+      <c r="M15" s="51" t="s">
+        <v>195</v>
+      </c>
+      <c r="N15" s="41" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5299,13 +5741,13 @@
         <v>97</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
@@ -5315,16 +5757,22 @@
       </c>
       <c r="H16" s="41"/>
       <c r="I16" s="42" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J16" s="41" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="K16" s="43" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L16" s="41" t="s">
-        <v>212</v>
+        <v>226</v>
+      </c>
+      <c r="M16" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="N16" s="41" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="29.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5332,13 +5780,13 @@
         <v>99</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="E17" s="39"/>
       <c r="F17" s="39"/>
@@ -5348,30 +5796,36 @@
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="42" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J17" s="41" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="K17" s="43" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L17" s="41" t="s">
-        <v>216</v>
+        <v>231</v>
+      </c>
+      <c r="M17" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="N17" s="41" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="40.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="50" t="s">
+      <c r="A18" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="51" t="s">
-        <v>217</v>
-      </c>
-      <c r="C18" s="52" t="s">
-        <v>218</v>
-      </c>
-      <c r="D18" s="51" t="s">
-        <v>219</v>
+      <c r="B18" s="53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="D18" s="53" t="s">
+        <v>235</v>
       </c>
       <c r="E18" s="39"/>
       <c r="F18" s="39"/>
@@ -5380,170 +5834,221 @@
         <v/>
       </c>
       <c r="H18" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="I18" s="53" t="s">
-        <v>221</v>
+        <v>236</v>
+      </c>
+      <c r="I18" s="55" t="s">
+        <v>237</v>
       </c>
       <c r="J18" s="41" t="s">
-        <v>222</v>
-      </c>
-      <c r="K18" s="44" t="s">
-        <v>174</v>
+        <v>238</v>
+      </c>
+      <c r="K18" s="45" t="s">
+        <v>178</v>
       </c>
       <c r="L18" s="41" t="s">
-        <v>223</v>
+        <v>239</v>
+      </c>
+      <c r="M18" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="N18" s="41" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="54"/>
+      <c r="A21" s="56"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="55" t="s">
-        <v>225</v>
+      <c r="A22" s="57" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="54"/>
+      <c r="A23" s="56" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="55" t="s">
-        <v>226</v>
+      <c r="A24" s="56" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="54" t="s">
-        <v>227</v>
+      <c r="A25" s="56" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="54" t="s">
-        <v>228</v>
+      <c r="A26" s="56" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="54" t="s">
-        <v>229</v>
-      </c>
+      <c r="A27" s="56"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="54" t="s">
-        <v>230</v>
+      <c r="A28" s="57" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="54"/>
+      <c r="A29" s="56" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="55" t="s">
-        <v>231</v>
+      <c r="A30" s="56" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="54" t="s">
-        <v>232</v>
+      <c r="A31" s="56" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="54" t="s">
-        <v>233</v>
-      </c>
+      <c r="A32" s="56"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="54" t="s">
-        <v>234</v>
+      <c r="A33" s="57" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="54" t="s">
-        <v>235</v>
+      <c r="A34" s="56" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="54"/>
+      <c r="A35" s="56" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="54" t="s">
-        <v>236</v>
+      <c r="A36" s="56" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="54" t="s">
-        <v>237</v>
+      <c r="A37" s="56" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="54"/>
+      <c r="A38" s="56" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="55" t="s">
-        <v>238</v>
+      <c r="A39" s="56" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="54" t="s">
-        <v>239</v>
-      </c>
+      <c r="A40" s="56"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="54" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="54" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="54" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="54" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="54" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="54"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="55" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="54" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="54" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="54" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="54"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="54" t="s">
-        <v>249</v>
+      <c r="A41" s="57" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="56" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="56" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="56" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="56" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="56" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="56" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="56" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="56" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="56"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="57" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="56" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="56" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="56" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="56"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="57" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="56" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="56" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="56" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="56"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="56" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
